--- a/artfynd/A 8924-2022 artfynd.xlsx
+++ b/artfynd/A 8924-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128375281</v>
       </c>
       <c r="B2" t="n">
-        <v>58503</v>
+        <v>58504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128375280</v>
       </c>
       <c r="B3" t="n">
-        <v>58531</v>
+        <v>58532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>128375279</v>
       </c>
       <c r="B4" t="n">
-        <v>58529</v>
+        <v>58530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8924-2022 artfynd.xlsx
+++ b/artfynd/A 8924-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128375281</v>
       </c>
       <c r="B2" t="n">
-        <v>58504</v>
+        <v>58516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128375280</v>
       </c>
       <c r="B3" t="n">
-        <v>58532</v>
+        <v>58544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>128375279</v>
       </c>
       <c r="B4" t="n">
-        <v>58530</v>
+        <v>58542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8924-2022 artfynd.xlsx
+++ b/artfynd/A 8924-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128375281</v>
       </c>
       <c r="B2" t="n">
-        <v>58516</v>
+        <v>58520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128375280</v>
       </c>
       <c r="B3" t="n">
-        <v>58544</v>
+        <v>58548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>128375279</v>
       </c>
       <c r="B4" t="n">
-        <v>58542</v>
+        <v>58546</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8924-2022 artfynd.xlsx
+++ b/artfynd/A 8924-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128375281</v>
       </c>
       <c r="B2" t="n">
-        <v>58520</v>
+        <v>58547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128375280</v>
       </c>
       <c r="B3" t="n">
-        <v>58548</v>
+        <v>58575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>128375279</v>
       </c>
       <c r="B4" t="n">
-        <v>58546</v>
+        <v>58573</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8924-2022 artfynd.xlsx
+++ b/artfynd/A 8924-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128375281</v>
       </c>
       <c r="B2" t="n">
-        <v>58547</v>
+        <v>58551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128375280</v>
       </c>
       <c r="B3" t="n">
-        <v>58575</v>
+        <v>58579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>128375279</v>
       </c>
       <c r="B4" t="n">
-        <v>58573</v>
+        <v>58577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8924-2022 artfynd.xlsx
+++ b/artfynd/A 8924-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128375281</v>
       </c>
       <c r="B2" t="n">
-        <v>58551</v>
+        <v>58554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128375280</v>
       </c>
       <c r="B3" t="n">
-        <v>58579</v>
+        <v>58582</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>128375279</v>
       </c>
       <c r="B4" t="n">
-        <v>58577</v>
+        <v>58580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8924-2022 artfynd.xlsx
+++ b/artfynd/A 8924-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128375281</v>
       </c>
       <c r="B2" t="n">
-        <v>58554</v>
+        <v>58790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128375280</v>
       </c>
       <c r="B3" t="n">
-        <v>58582</v>
+        <v>58817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>128375279</v>
       </c>
       <c r="B4" t="n">
-        <v>58580</v>
+        <v>58815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
